--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128340203</v>
+        <v>128340171</v>
       </c>
       <c r="B12" t="n">
-        <v>92754</v>
+        <v>92730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>149</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405854</v>
+        <v>406179</v>
       </c>
       <c r="R12" t="n">
-        <v>6854526</v>
+        <v>6854239</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1856,32 +1856,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128340200</v>
+        <v>128340203</v>
       </c>
       <c r="B13" t="n">
-        <v>92736</v>
+        <v>92754</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,13 +1895,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405959</v>
+        <v>405854</v>
       </c>
       <c r="R13" t="n">
-        <v>6854436</v>
+        <v>6854526</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1962,32 +1962,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128340171</v>
+        <v>128340200</v>
       </c>
       <c r="B14" t="n">
-        <v>92730</v>
+        <v>92736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406179</v>
+        <v>405959</v>
       </c>
       <c r="R14" t="n">
-        <v>6854239</v>
+        <v>6854436</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -3552,32 +3552,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128533313</v>
+        <v>128533093</v>
       </c>
       <c r="B29" t="n">
-        <v>92767</v>
+        <v>92742</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3591,13 +3591,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>406072</v>
+        <v>406203</v>
       </c>
       <c r="R29" t="n">
-        <v>6853922</v>
+        <v>6853655</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3621,12 +3621,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3658,32 +3658,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128533093</v>
+        <v>128533313</v>
       </c>
       <c r="B30" t="n">
-        <v>92742</v>
+        <v>92767</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3697,13 +3697,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>406203</v>
+        <v>406072</v>
       </c>
       <c r="R30" t="n">
-        <v>6853655</v>
+        <v>6853922</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">

--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128340171</v>
+        <v>128340200</v>
       </c>
       <c r="B12" t="n">
-        <v>92730</v>
+        <v>92736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406179</v>
+        <v>405959</v>
       </c>
       <c r="R12" t="n">
-        <v>6854239</v>
+        <v>6854436</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1856,32 +1856,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128340203</v>
+        <v>128340171</v>
       </c>
       <c r="B13" t="n">
-        <v>92754</v>
+        <v>92730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>149</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,13 +1895,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405854</v>
+        <v>406179</v>
       </c>
       <c r="R13" t="n">
-        <v>6854526</v>
+        <v>6854239</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1962,32 +1962,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128340200</v>
+        <v>128340203</v>
       </c>
       <c r="B14" t="n">
-        <v>92736</v>
+        <v>92754</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405959</v>
+        <v>405854</v>
       </c>
       <c r="R14" t="n">
-        <v>6854436</v>
+        <v>6854526</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -2389,7 +2389,7 @@
         <v>128533304</v>
       </c>
       <c r="B18" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>128533095</v>
       </c>
       <c r="B19" t="n">
-        <v>92736</v>
+        <v>92742</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>128533314</v>
       </c>
       <c r="B20" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>128533312</v>
       </c>
       <c r="B21" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>128533094</v>
       </c>
       <c r="B22" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>128533306</v>
       </c>
       <c r="B23" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>128533307</v>
       </c>
       <c r="B24" t="n">
-        <v>92736</v>
+        <v>92742</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>128533310</v>
       </c>
       <c r="B25" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128533311</v>
       </c>
       <c r="B26" t="n">
-        <v>92736</v>
+        <v>92742</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>128533308</v>
       </c>
       <c r="B27" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>128533305</v>
       </c>
       <c r="B28" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>128533093</v>
       </c>
       <c r="B29" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>128533313</v>
       </c>
       <c r="B30" t="n">
-        <v>92767</v>
+        <v>92773</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>128533303</v>
       </c>
       <c r="B31" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128340197</v>
       </c>
       <c r="B5" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>128340202</v>
       </c>
       <c r="B6" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>128340198</v>
       </c>
       <c r="B7" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>128340194</v>
       </c>
       <c r="B8" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>128340195</v>
       </c>
       <c r="B9" t="n">
-        <v>92736</v>
+        <v>92748</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>128340172</v>
       </c>
       <c r="B10" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>128340201</v>
       </c>
       <c r="B11" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128340200</v>
+        <v>128340203</v>
       </c>
       <c r="B12" t="n">
-        <v>92736</v>
+        <v>92766</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405959</v>
+        <v>405854</v>
       </c>
       <c r="R12" t="n">
-        <v>6854436</v>
+        <v>6854526</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1856,32 +1856,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128340171</v>
+        <v>128340200</v>
       </c>
       <c r="B13" t="n">
-        <v>92730</v>
+        <v>92748</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,13 +1895,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406179</v>
+        <v>405959</v>
       </c>
       <c r="R13" t="n">
-        <v>6854239</v>
+        <v>6854436</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1962,32 +1962,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128340203</v>
+        <v>128340171</v>
       </c>
       <c r="B14" t="n">
-        <v>92754</v>
+        <v>92742</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>149</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405854</v>
+        <v>406179</v>
       </c>
       <c r="R14" t="n">
-        <v>6854526</v>
+        <v>6854239</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>128340254</v>
       </c>
       <c r="B15" t="n">
-        <v>92736</v>
+        <v>92748</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>128340199</v>
       </c>
       <c r="B16" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>128340196</v>
       </c>
       <c r="B17" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2386,32 +2386,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128533304</v>
+        <v>128533095</v>
       </c>
       <c r="B18" t="n">
         <v>92748</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406143</v>
+        <v>406173</v>
       </c>
       <c r="R18" t="n">
-        <v>6853912</v>
+        <v>6853701</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2455,12 +2455,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2492,32 +2492,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128533095</v>
+        <v>128533304</v>
       </c>
       <c r="B19" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406173</v>
+        <v>406143</v>
       </c>
       <c r="R19" t="n">
-        <v>6853701</v>
+        <v>6853912</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2598,10 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128533314</v>
+        <v>128533312</v>
       </c>
       <c r="B20" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2637,13 +2637,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406084</v>
+        <v>406071</v>
       </c>
       <c r="R20" t="n">
-        <v>6853954</v>
+        <v>6853933</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128533312</v>
+        <v>128533314</v>
       </c>
       <c r="B21" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406071</v>
+        <v>406084</v>
       </c>
       <c r="R21" t="n">
-        <v>6853933</v>
+        <v>6853954</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>128533094</v>
       </c>
       <c r="B22" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>128533306</v>
       </c>
       <c r="B23" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3022,32 +3022,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128533307</v>
+        <v>128533310</v>
       </c>
       <c r="B24" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>406344</v>
+        <v>406063</v>
       </c>
       <c r="R24" t="n">
-        <v>6854164</v>
+        <v>6853825</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3128,32 +3128,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128533310</v>
+        <v>128533307</v>
       </c>
       <c r="B25" t="n">
         <v>92748</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>406063</v>
+        <v>406344</v>
       </c>
       <c r="R25" t="n">
-        <v>6853825</v>
+        <v>6854164</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3237,7 +3237,7 @@
         <v>128533311</v>
       </c>
       <c r="B26" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3340,10 +3340,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128533308</v>
+        <v>128533305</v>
       </c>
       <c r="B27" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>406061</v>
+        <v>406193</v>
       </c>
       <c r="R27" t="n">
-        <v>6853845</v>
+        <v>6853944</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3446,10 +3446,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128533305</v>
+        <v>128533308</v>
       </c>
       <c r="B28" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>406193</v>
+        <v>406061</v>
       </c>
       <c r="R28" t="n">
-        <v>6853944</v>
+        <v>6853845</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3552,32 +3552,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128533093</v>
+        <v>128533313</v>
       </c>
       <c r="B29" t="n">
-        <v>92748</v>
+        <v>92779</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3591,13 +3591,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>406203</v>
+        <v>406072</v>
       </c>
       <c r="R29" t="n">
-        <v>6853655</v>
+        <v>6853922</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3621,12 +3621,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3658,32 +3658,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128533313</v>
+        <v>128533093</v>
       </c>
       <c r="B30" t="n">
-        <v>92773</v>
+        <v>92754</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3697,13 +3697,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>406072</v>
+        <v>406203</v>
       </c>
       <c r="R30" t="n">
-        <v>6853922</v>
+        <v>6853655</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3767,7 +3767,7 @@
         <v>128533303</v>
       </c>
       <c r="B31" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128340203</v>
+        <v>128340200</v>
       </c>
       <c r="B12" t="n">
-        <v>92766</v>
+        <v>92748</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405854</v>
+        <v>405959</v>
       </c>
       <c r="R12" t="n">
-        <v>6854526</v>
+        <v>6854436</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1856,32 +1856,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128340200</v>
+        <v>128340171</v>
       </c>
       <c r="B13" t="n">
-        <v>92748</v>
+        <v>92742</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,13 +1895,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405959</v>
+        <v>406179</v>
       </c>
       <c r="R13" t="n">
-        <v>6854436</v>
+        <v>6854239</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1962,32 +1962,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128340171</v>
+        <v>128340203</v>
       </c>
       <c r="B14" t="n">
-        <v>92742</v>
+        <v>92766</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406179</v>
+        <v>405854</v>
       </c>
       <c r="R14" t="n">
-        <v>6854239</v>
+        <v>6854526</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128340197</v>
       </c>
       <c r="B5" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>128340202</v>
       </c>
       <c r="B6" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>128340198</v>
       </c>
       <c r="B7" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>128340194</v>
       </c>
       <c r="B8" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>128340195</v>
       </c>
       <c r="B9" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>128340172</v>
       </c>
       <c r="B10" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>128340201</v>
       </c>
       <c r="B11" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128340200</v>
+        <v>128340171</v>
       </c>
       <c r="B12" t="n">
-        <v>92748</v>
+        <v>92744</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405959</v>
+        <v>406179</v>
       </c>
       <c r="R12" t="n">
-        <v>6854436</v>
+        <v>6854239</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1856,32 +1856,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128340171</v>
+        <v>128340200</v>
       </c>
       <c r="B13" t="n">
-        <v>92742</v>
+        <v>92750</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,13 +1895,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406179</v>
+        <v>405959</v>
       </c>
       <c r="R13" t="n">
-        <v>6854239</v>
+        <v>6854436</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>128340203</v>
       </c>
       <c r="B14" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>128340254</v>
       </c>
       <c r="B15" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>128340199</v>
       </c>
       <c r="B16" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>128340196</v>
       </c>
       <c r="B17" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2386,32 +2386,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128533095</v>
+        <v>128533304</v>
       </c>
       <c r="B18" t="n">
-        <v>92748</v>
+        <v>92756</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406173</v>
+        <v>406143</v>
       </c>
       <c r="R18" t="n">
-        <v>6853701</v>
+        <v>6853912</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2455,12 +2455,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2492,32 +2492,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128533304</v>
+        <v>128533095</v>
       </c>
       <c r="B19" t="n">
-        <v>92754</v>
+        <v>92750</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406143</v>
+        <v>406173</v>
       </c>
       <c r="R19" t="n">
-        <v>6853912</v>
+        <v>6853701</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2598,10 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128533312</v>
+        <v>128533314</v>
       </c>
       <c r="B20" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2637,13 +2637,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406071</v>
+        <v>406084</v>
       </c>
       <c r="R20" t="n">
-        <v>6853933</v>
+        <v>6853954</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128533314</v>
+        <v>128533312</v>
       </c>
       <c r="B21" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406084</v>
+        <v>406071</v>
       </c>
       <c r="R21" t="n">
-        <v>6853954</v>
+        <v>6853933</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>128533094</v>
       </c>
       <c r="B22" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>128533306</v>
       </c>
       <c r="B23" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3022,32 +3022,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128533310</v>
+        <v>128533307</v>
       </c>
       <c r="B24" t="n">
-        <v>92754</v>
+        <v>92750</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>406063</v>
+        <v>406344</v>
       </c>
       <c r="R24" t="n">
-        <v>6853825</v>
+        <v>6854164</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3128,32 +3128,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128533307</v>
+        <v>128533310</v>
       </c>
       <c r="B25" t="n">
-        <v>92748</v>
+        <v>92756</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>406344</v>
+        <v>406063</v>
       </c>
       <c r="R25" t="n">
-        <v>6854164</v>
+        <v>6853825</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3237,7 +3237,7 @@
         <v>128533311</v>
       </c>
       <c r="B26" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3340,10 +3340,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128533305</v>
+        <v>128533308</v>
       </c>
       <c r="B27" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>406193</v>
+        <v>406061</v>
       </c>
       <c r="R27" t="n">
-        <v>6853944</v>
+        <v>6853845</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3446,10 +3446,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128533308</v>
+        <v>128533305</v>
       </c>
       <c r="B28" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>406061</v>
+        <v>406193</v>
       </c>
       <c r="R28" t="n">
-        <v>6853845</v>
+        <v>6853944</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3555,7 +3555,7 @@
         <v>128533313</v>
       </c>
       <c r="B29" t="n">
-        <v>92779</v>
+        <v>92781</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>128533093</v>
       </c>
       <c r="B30" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>128533303</v>
       </c>
       <c r="B31" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128340171</v>
+        <v>128340203</v>
       </c>
       <c r="B12" t="n">
-        <v>92744</v>
+        <v>92768</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406179</v>
+        <v>405854</v>
       </c>
       <c r="R12" t="n">
-        <v>6854239</v>
+        <v>6854526</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1962,32 +1962,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128340203</v>
+        <v>128340171</v>
       </c>
       <c r="B14" t="n">
-        <v>92768</v>
+        <v>92744</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>149</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405854</v>
+        <v>406179</v>
       </c>
       <c r="R14" t="n">
-        <v>6854526</v>
+        <v>6854239</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128340203</v>
+        <v>128340171</v>
       </c>
       <c r="B12" t="n">
-        <v>92768</v>
+        <v>92744</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>149</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405854</v>
+        <v>406179</v>
       </c>
       <c r="R12" t="n">
-        <v>6854526</v>
+        <v>6854239</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1856,32 +1856,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128340200</v>
+        <v>128340203</v>
       </c>
       <c r="B13" t="n">
-        <v>92750</v>
+        <v>92768</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,13 +1895,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405959</v>
+        <v>405854</v>
       </c>
       <c r="R13" t="n">
-        <v>6854436</v>
+        <v>6854526</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1962,32 +1962,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128340171</v>
+        <v>128340200</v>
       </c>
       <c r="B14" t="n">
-        <v>92744</v>
+        <v>92750</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406179</v>
+        <v>405959</v>
       </c>
       <c r="R14" t="n">
-        <v>6854239</v>
+        <v>6854436</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128340197</v>
       </c>
       <c r="B5" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>128340202</v>
       </c>
       <c r="B6" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>128340198</v>
       </c>
       <c r="B7" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>128340194</v>
       </c>
       <c r="B8" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>128340195</v>
       </c>
       <c r="B9" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>128340172</v>
       </c>
       <c r="B10" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>128340201</v>
       </c>
       <c r="B11" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128340171</v>
+        <v>128340203</v>
       </c>
       <c r="B12" t="n">
-        <v>92744</v>
+        <v>92769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406179</v>
+        <v>405854</v>
       </c>
       <c r="R12" t="n">
-        <v>6854239</v>
+        <v>6854526</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1856,32 +1856,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128340203</v>
+        <v>128340200</v>
       </c>
       <c r="B13" t="n">
-        <v>92768</v>
+        <v>92751</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,13 +1895,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405854</v>
+        <v>405959</v>
       </c>
       <c r="R13" t="n">
-        <v>6854526</v>
+        <v>6854436</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1962,32 +1962,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128340200</v>
+        <v>128340171</v>
       </c>
       <c r="B14" t="n">
-        <v>92750</v>
+        <v>92745</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405959</v>
+        <v>406179</v>
       </c>
       <c r="R14" t="n">
-        <v>6854436</v>
+        <v>6854239</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>128340254</v>
       </c>
       <c r="B15" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>128340199</v>
       </c>
       <c r="B16" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>128340196</v>
       </c>
       <c r="B17" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2386,32 +2386,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128533304</v>
+        <v>128533095</v>
       </c>
       <c r="B18" t="n">
-        <v>92756</v>
+        <v>92751</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406143</v>
+        <v>406173</v>
       </c>
       <c r="R18" t="n">
-        <v>6853912</v>
+        <v>6853701</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2455,12 +2455,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2492,32 +2492,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128533095</v>
+        <v>128533304</v>
       </c>
       <c r="B19" t="n">
-        <v>92750</v>
+        <v>92757</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406173</v>
+        <v>406143</v>
       </c>
       <c r="R19" t="n">
-        <v>6853701</v>
+        <v>6853912</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2598,10 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128533314</v>
+        <v>128533312</v>
       </c>
       <c r="B20" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2637,13 +2637,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406084</v>
+        <v>406071</v>
       </c>
       <c r="R20" t="n">
-        <v>6853954</v>
+        <v>6853933</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128533312</v>
+        <v>128533314</v>
       </c>
       <c r="B21" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406071</v>
+        <v>406084</v>
       </c>
       <c r="R21" t="n">
-        <v>6853933</v>
+        <v>6853954</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>128533094</v>
       </c>
       <c r="B22" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>128533306</v>
       </c>
       <c r="B23" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3022,32 +3022,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128533307</v>
+        <v>128533310</v>
       </c>
       <c r="B24" t="n">
-        <v>92750</v>
+        <v>92757</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>406344</v>
+        <v>406063</v>
       </c>
       <c r="R24" t="n">
-        <v>6854164</v>
+        <v>6853825</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3128,32 +3128,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128533310</v>
+        <v>128533307</v>
       </c>
       <c r="B25" t="n">
-        <v>92756</v>
+        <v>92751</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>406063</v>
+        <v>406344</v>
       </c>
       <c r="R25" t="n">
-        <v>6853825</v>
+        <v>6854164</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3237,7 +3237,7 @@
         <v>128533311</v>
       </c>
       <c r="B26" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>128533308</v>
       </c>
       <c r="B27" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>128533305</v>
       </c>
       <c r="B28" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>128533313</v>
       </c>
       <c r="B29" t="n">
-        <v>92781</v>
+        <v>92782</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>128533093</v>
       </c>
       <c r="B30" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>128533303</v>
       </c>
       <c r="B31" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -2389,7 +2389,7 @@
         <v>128533095</v>
       </c>
       <c r="B18" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>128533304</v>
       </c>
       <c r="B19" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>128533312</v>
       </c>
       <c r="B20" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>128533314</v>
       </c>
       <c r="B21" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>128533094</v>
       </c>
       <c r="B22" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>128533306</v>
       </c>
       <c r="B23" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>128533310</v>
       </c>
       <c r="B24" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>128533307</v>
       </c>
       <c r="B25" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128533311</v>
       </c>
       <c r="B26" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3340,10 +3340,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128533308</v>
+        <v>128533305</v>
       </c>
       <c r="B27" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>406061</v>
+        <v>406193</v>
       </c>
       <c r="R27" t="n">
-        <v>6853845</v>
+        <v>6853944</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3446,10 +3446,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128533305</v>
+        <v>128533308</v>
       </c>
       <c r="B28" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>406193</v>
+        <v>406061</v>
       </c>
       <c r="R28" t="n">
-        <v>6853944</v>
+        <v>6853845</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3555,7 +3555,7 @@
         <v>128533313</v>
       </c>
       <c r="B29" t="n">
-        <v>92782</v>
+        <v>92809</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>128533093</v>
       </c>
       <c r="B30" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>128533303</v>
       </c>
       <c r="B31" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128340197</v>
       </c>
       <c r="B5" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>128340202</v>
       </c>
       <c r="B6" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>128340198</v>
       </c>
       <c r="B7" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>128340194</v>
       </c>
       <c r="B8" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>128340195</v>
       </c>
       <c r="B9" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>128340172</v>
       </c>
       <c r="B10" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>128340201</v>
       </c>
       <c r="B11" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128340203</v>
+        <v>128340200</v>
       </c>
       <c r="B12" t="n">
-        <v>92769</v>
+        <v>92778</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405854</v>
+        <v>405959</v>
       </c>
       <c r="R12" t="n">
-        <v>6854526</v>
+        <v>6854436</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1856,32 +1856,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128340200</v>
+        <v>128340171</v>
       </c>
       <c r="B13" t="n">
-        <v>92751</v>
+        <v>92772</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,13 +1895,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405959</v>
+        <v>406179</v>
       </c>
       <c r="R13" t="n">
-        <v>6854436</v>
+        <v>6854239</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1962,32 +1962,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128340171</v>
+        <v>128340203</v>
       </c>
       <c r="B14" t="n">
-        <v>92745</v>
+        <v>92796</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406179</v>
+        <v>405854</v>
       </c>
       <c r="R14" t="n">
-        <v>6854239</v>
+        <v>6854526</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>128340254</v>
       </c>
       <c r="B15" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>128340199</v>
       </c>
       <c r="B16" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>128340196</v>
       </c>
       <c r="B17" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -1114,7 +1114,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128340202</v>
+        <v>128340198</v>
       </c>
       <c r="B6" t="n">
         <v>92796</v>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405933</v>
+        <v>405940</v>
       </c>
       <c r="R6" t="n">
-        <v>6854502</v>
+        <v>6854358</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128340198</v>
+        <v>128340202</v>
       </c>
       <c r="B7" t="n">
         <v>92796</v>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405940</v>
+        <v>405933</v>
       </c>
       <c r="R7" t="n">
-        <v>6854358</v>
+        <v>6854502</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128340200</v>
+        <v>128340203</v>
       </c>
       <c r="B12" t="n">
-        <v>92778</v>
+        <v>92796</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405959</v>
+        <v>405854</v>
       </c>
       <c r="R12" t="n">
-        <v>6854436</v>
+        <v>6854526</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1856,32 +1856,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128340171</v>
+        <v>128340200</v>
       </c>
       <c r="B13" t="n">
-        <v>92772</v>
+        <v>92778</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,13 +1895,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406179</v>
+        <v>405959</v>
       </c>
       <c r="R13" t="n">
-        <v>6854239</v>
+        <v>6854436</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1962,32 +1962,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128340203</v>
+        <v>128340171</v>
       </c>
       <c r="B14" t="n">
-        <v>92796</v>
+        <v>92772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>149</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405854</v>
+        <v>406179</v>
       </c>
       <c r="R14" t="n">
-        <v>6854526</v>
+        <v>6854239</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2068,32 +2068,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128340254</v>
+        <v>128340199</v>
       </c>
       <c r="B15" t="n">
-        <v>92778</v>
+        <v>92796</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406282</v>
+        <v>405994</v>
       </c>
       <c r="R15" t="n">
-        <v>6854370</v>
+        <v>6854403</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2137,12 +2137,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2174,32 +2174,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128340199</v>
+        <v>128340254</v>
       </c>
       <c r="B16" t="n">
-        <v>92796</v>
+        <v>92778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405994</v>
+        <v>406282</v>
       </c>
       <c r="R16" t="n">
-        <v>6854403</v>
+        <v>6854370</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2243,12 +2243,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2389,7 +2389,7 @@
         <v>128533095</v>
       </c>
       <c r="B18" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>128533304</v>
       </c>
       <c r="B19" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>128533312</v>
       </c>
       <c r="B20" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>128533314</v>
       </c>
       <c r="B21" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>128533094</v>
       </c>
       <c r="B22" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>128533306</v>
       </c>
       <c r="B23" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>128533310</v>
       </c>
       <c r="B24" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>128533307</v>
       </c>
       <c r="B25" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128533311</v>
       </c>
       <c r="B26" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>128533305</v>
       </c>
       <c r="B27" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>128533308</v>
       </c>
       <c r="B28" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>128533313</v>
       </c>
       <c r="B29" t="n">
-        <v>92809</v>
+        <v>92814</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>128533093</v>
       </c>
       <c r="B30" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>128533303</v>
       </c>
       <c r="B31" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128340197</v>
       </c>
       <c r="B5" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>128340198</v>
       </c>
       <c r="B6" t="n">
-        <v>92796</v>
+        <v>92806</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>128340202</v>
       </c>
       <c r="B7" t="n">
-        <v>92796</v>
+        <v>92806</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>128340194</v>
       </c>
       <c r="B8" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>128340195</v>
       </c>
       <c r="B9" t="n">
-        <v>92778</v>
+        <v>92788</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>128340172</v>
       </c>
       <c r="B10" t="n">
-        <v>92796</v>
+        <v>92806</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>128340201</v>
       </c>
       <c r="B11" t="n">
-        <v>92796</v>
+        <v>92806</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128340203</v>
+        <v>128340200</v>
       </c>
       <c r="B12" t="n">
-        <v>92796</v>
+        <v>92788</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405854</v>
+        <v>405959</v>
       </c>
       <c r="R12" t="n">
-        <v>6854526</v>
+        <v>6854436</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1856,32 +1856,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128340200</v>
+        <v>128340171</v>
       </c>
       <c r="B13" t="n">
-        <v>92778</v>
+        <v>92782</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,13 +1895,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405959</v>
+        <v>406179</v>
       </c>
       <c r="R13" t="n">
-        <v>6854436</v>
+        <v>6854239</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1962,32 +1962,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128340171</v>
+        <v>128340203</v>
       </c>
       <c r="B14" t="n">
-        <v>92772</v>
+        <v>92806</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406179</v>
+        <v>405854</v>
       </c>
       <c r="R14" t="n">
-        <v>6854239</v>
+        <v>6854526</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>128340199</v>
       </c>
       <c r="B15" t="n">
-        <v>92796</v>
+        <v>92806</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>128340254</v>
       </c>
       <c r="B16" t="n">
-        <v>92778</v>
+        <v>92788</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>128340196</v>
       </c>
       <c r="B17" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2386,32 +2386,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128533095</v>
+        <v>128533304</v>
       </c>
       <c r="B18" t="n">
-        <v>92783</v>
+        <v>92794</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406173</v>
+        <v>406143</v>
       </c>
       <c r="R18" t="n">
-        <v>6853701</v>
+        <v>6853912</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2455,12 +2455,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2492,32 +2492,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128533304</v>
+        <v>128533095</v>
       </c>
       <c r="B19" t="n">
-        <v>92789</v>
+        <v>92788</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406143</v>
+        <v>406173</v>
       </c>
       <c r="R19" t="n">
-        <v>6853912</v>
+        <v>6853701</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2598,10 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128533312</v>
+        <v>128533314</v>
       </c>
       <c r="B20" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2637,13 +2637,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406071</v>
+        <v>406084</v>
       </c>
       <c r="R20" t="n">
-        <v>6853933</v>
+        <v>6853954</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128533314</v>
+        <v>128533312</v>
       </c>
       <c r="B21" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406084</v>
+        <v>406071</v>
       </c>
       <c r="R21" t="n">
-        <v>6853954</v>
+        <v>6853933</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>128533094</v>
       </c>
       <c r="B22" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>128533306</v>
       </c>
       <c r="B23" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3022,32 +3022,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128533310</v>
+        <v>128533307</v>
       </c>
       <c r="B24" t="n">
-        <v>92789</v>
+        <v>92788</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>406063</v>
+        <v>406344</v>
       </c>
       <c r="R24" t="n">
-        <v>6853825</v>
+        <v>6854164</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3128,32 +3128,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128533307</v>
+        <v>128533310</v>
       </c>
       <c r="B25" t="n">
-        <v>92783</v>
+        <v>92794</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>406344</v>
+        <v>406063</v>
       </c>
       <c r="R25" t="n">
-        <v>6854164</v>
+        <v>6853825</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3237,7 +3237,7 @@
         <v>128533311</v>
       </c>
       <c r="B26" t="n">
-        <v>92783</v>
+        <v>92788</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3340,10 +3340,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128533305</v>
+        <v>128533308</v>
       </c>
       <c r="B27" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>406193</v>
+        <v>406061</v>
       </c>
       <c r="R27" t="n">
-        <v>6853944</v>
+        <v>6853845</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3446,10 +3446,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128533308</v>
+        <v>128533305</v>
       </c>
       <c r="B28" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>406061</v>
+        <v>406193</v>
       </c>
       <c r="R28" t="n">
-        <v>6853845</v>
+        <v>6853944</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3552,32 +3552,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128533313</v>
+        <v>128533093</v>
       </c>
       <c r="B29" t="n">
-        <v>92814</v>
+        <v>92794</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3591,13 +3591,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>406072</v>
+        <v>406203</v>
       </c>
       <c r="R29" t="n">
-        <v>6853922</v>
+        <v>6853655</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3621,12 +3621,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3658,32 +3658,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128533093</v>
+        <v>128533313</v>
       </c>
       <c r="B30" t="n">
-        <v>92789</v>
+        <v>92819</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3697,13 +3697,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>406203</v>
+        <v>406072</v>
       </c>
       <c r="R30" t="n">
-        <v>6853655</v>
+        <v>6853922</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3767,7 +3767,7 @@
         <v>128533303</v>
       </c>
       <c r="B31" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128340200</v>
+        <v>128340203</v>
       </c>
       <c r="B12" t="n">
-        <v>92788</v>
+        <v>92806</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405959</v>
+        <v>405854</v>
       </c>
       <c r="R12" t="n">
-        <v>6854436</v>
+        <v>6854526</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1962,32 +1962,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128340203</v>
+        <v>128340200</v>
       </c>
       <c r="B14" t="n">
-        <v>92806</v>
+        <v>92788</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405854</v>
+        <v>405959</v>
       </c>
       <c r="R14" t="n">
-        <v>6854526</v>
+        <v>6854436</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -3552,32 +3552,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128533093</v>
+        <v>128533313</v>
       </c>
       <c r="B29" t="n">
-        <v>92794</v>
+        <v>92819</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3591,13 +3591,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>406203</v>
+        <v>406072</v>
       </c>
       <c r="R29" t="n">
-        <v>6853655</v>
+        <v>6853922</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3621,12 +3621,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3658,32 +3658,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128533313</v>
+        <v>128533093</v>
       </c>
       <c r="B30" t="n">
-        <v>92819</v>
+        <v>92794</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3697,13 +3697,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>406072</v>
+        <v>406203</v>
       </c>
       <c r="R30" t="n">
-        <v>6853922</v>
+        <v>6853655</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">

--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -1856,32 +1856,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128340171</v>
+        <v>128340200</v>
       </c>
       <c r="B13" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,13 +1895,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406179</v>
+        <v>405959</v>
       </c>
       <c r="R13" t="n">
-        <v>6854239</v>
+        <v>6854436</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1962,32 +1962,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128340200</v>
+        <v>128340171</v>
       </c>
       <c r="B14" t="n">
-        <v>92788</v>
+        <v>92782</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405959</v>
+        <v>406179</v>
       </c>
       <c r="R14" t="n">
-        <v>6854436</v>
+        <v>6854239</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -1114,7 +1114,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128340198</v>
+        <v>128340202</v>
       </c>
       <c r="B6" t="n">
         <v>92806</v>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405940</v>
+        <v>405933</v>
       </c>
       <c r="R6" t="n">
-        <v>6854358</v>
+        <v>6854502</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128340202</v>
+        <v>128340198</v>
       </c>
       <c r="B7" t="n">
         <v>92806</v>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405933</v>
+        <v>405940</v>
       </c>
       <c r="R7" t="n">
-        <v>6854502</v>
+        <v>6854358</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128340203</v>
+        <v>128340171</v>
       </c>
       <c r="B12" t="n">
-        <v>92806</v>
+        <v>92782</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>149</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405854</v>
+        <v>406179</v>
       </c>
       <c r="R12" t="n">
-        <v>6854526</v>
+        <v>6854239</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1856,32 +1856,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128340200</v>
+        <v>128340203</v>
       </c>
       <c r="B13" t="n">
-        <v>92788</v>
+        <v>92806</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,13 +1895,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405959</v>
+        <v>405854</v>
       </c>
       <c r="R13" t="n">
-        <v>6854436</v>
+        <v>6854526</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1962,32 +1962,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128340171</v>
+        <v>128340200</v>
       </c>
       <c r="B14" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406179</v>
+        <v>405959</v>
       </c>
       <c r="R14" t="n">
-        <v>6854239</v>
+        <v>6854436</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2068,32 +2068,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128340199</v>
+        <v>128340254</v>
       </c>
       <c r="B15" t="n">
-        <v>92806</v>
+        <v>92788</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405994</v>
+        <v>406282</v>
       </c>
       <c r="R15" t="n">
-        <v>6854403</v>
+        <v>6854370</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2137,12 +2137,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2174,32 +2174,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128340254</v>
+        <v>128340199</v>
       </c>
       <c r="B16" t="n">
-        <v>92788</v>
+        <v>92806</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406282</v>
+        <v>405994</v>
       </c>
       <c r="R16" t="n">
-        <v>6854370</v>
+        <v>6854403</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2243,12 +2243,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2389,7 +2389,7 @@
         <v>128533304</v>
       </c>
       <c r="B18" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>128533095</v>
       </c>
       <c r="B19" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>128533314</v>
       </c>
       <c r="B20" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>128533312</v>
       </c>
       <c r="B21" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>128533094</v>
       </c>
       <c r="B22" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>128533306</v>
       </c>
       <c r="B23" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>128533307</v>
       </c>
       <c r="B24" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>128533310</v>
       </c>
       <c r="B25" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128533311</v>
       </c>
       <c r="B26" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>128533308</v>
       </c>
       <c r="B27" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>128533305</v>
       </c>
       <c r="B28" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>128533313</v>
       </c>
       <c r="B29" t="n">
-        <v>92819</v>
+        <v>92823</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>128533093</v>
       </c>
       <c r="B30" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>128533303</v>
       </c>
       <c r="B31" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128340197</v>
       </c>
       <c r="B5" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>128340202</v>
       </c>
       <c r="B6" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>128340198</v>
       </c>
       <c r="B7" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>128340194</v>
       </c>
       <c r="B8" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>128340195</v>
       </c>
       <c r="B9" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>128340172</v>
       </c>
       <c r="B10" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>128340201</v>
       </c>
       <c r="B11" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128340171</v>
+        <v>128340203</v>
       </c>
       <c r="B12" t="n">
-        <v>92782</v>
+        <v>92810</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406179</v>
+        <v>405854</v>
       </c>
       <c r="R12" t="n">
-        <v>6854239</v>
+        <v>6854526</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1856,32 +1856,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128340203</v>
+        <v>128340200</v>
       </c>
       <c r="B13" t="n">
-        <v>92806</v>
+        <v>92792</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,13 +1895,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405854</v>
+        <v>405959</v>
       </c>
       <c r="R13" t="n">
-        <v>6854526</v>
+        <v>6854436</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1962,32 +1962,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128340200</v>
+        <v>128340171</v>
       </c>
       <c r="B14" t="n">
-        <v>92788</v>
+        <v>92786</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405959</v>
+        <v>406179</v>
       </c>
       <c r="R14" t="n">
-        <v>6854436</v>
+        <v>6854239</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>128340254</v>
       </c>
       <c r="B15" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>128340199</v>
       </c>
       <c r="B16" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>128340196</v>
       </c>
       <c r="B17" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128533308</v>
+        <v>128533305</v>
       </c>
       <c r="B27" t="n">
         <v>92810</v>
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>406061</v>
+        <v>406193</v>
       </c>
       <c r="R27" t="n">
-        <v>6853845</v>
+        <v>6853944</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128533305</v>
+        <v>128533308</v>
       </c>
       <c r="B28" t="n">
         <v>92810</v>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>406193</v>
+        <v>406061</v>
       </c>
       <c r="R28" t="n">
-        <v>6853944</v>
+        <v>6853845</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>

--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -3340,7 +3340,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128533305</v>
+        <v>128533308</v>
       </c>
       <c r="B27" t="n">
         <v>92810</v>
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>406193</v>
+        <v>406061</v>
       </c>
       <c r="R27" t="n">
-        <v>6853944</v>
+        <v>6853845</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128533308</v>
+        <v>128533305</v>
       </c>
       <c r="B28" t="n">
         <v>92810</v>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>406061</v>
+        <v>406193</v>
       </c>
       <c r="R28" t="n">
-        <v>6853845</v>
+        <v>6853944</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3552,32 +3552,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128533313</v>
+        <v>128533093</v>
       </c>
       <c r="B29" t="n">
-        <v>92823</v>
+        <v>92798</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3591,13 +3591,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>406072</v>
+        <v>406203</v>
       </c>
       <c r="R29" t="n">
-        <v>6853922</v>
+        <v>6853655</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3621,12 +3621,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3658,32 +3658,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128533093</v>
+        <v>128533313</v>
       </c>
       <c r="B30" t="n">
-        <v>92798</v>
+        <v>92823</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3697,13 +3697,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>406203</v>
+        <v>406072</v>
       </c>
       <c r="R30" t="n">
-        <v>6853655</v>
+        <v>6853922</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">

--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -2389,7 +2389,7 @@
         <v>128533304</v>
       </c>
       <c r="B18" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>128533095</v>
       </c>
       <c r="B19" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>128533314</v>
       </c>
       <c r="B20" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>128533312</v>
       </c>
       <c r="B21" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>128533094</v>
       </c>
       <c r="B22" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>128533306</v>
       </c>
       <c r="B23" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>128533307</v>
       </c>
       <c r="B24" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>128533310</v>
       </c>
       <c r="B25" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128533311</v>
       </c>
       <c r="B26" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>128533308</v>
       </c>
       <c r="B27" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>128533305</v>
       </c>
       <c r="B28" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>128533093</v>
       </c>
       <c r="B29" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>128533313</v>
       </c>
       <c r="B30" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>128533303</v>
       </c>
       <c r="B31" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -2386,32 +2386,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128533304</v>
+        <v>128533095</v>
       </c>
       <c r="B18" t="n">
-        <v>92806</v>
+        <v>92805</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406143</v>
+        <v>406173</v>
       </c>
       <c r="R18" t="n">
-        <v>6853912</v>
+        <v>6853701</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2455,12 +2455,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2492,32 +2492,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128533095</v>
+        <v>128533304</v>
       </c>
       <c r="B19" t="n">
-        <v>92800</v>
+        <v>92811</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406173</v>
+        <v>406143</v>
       </c>
       <c r="R19" t="n">
-        <v>6853701</v>
+        <v>6853912</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2601,7 +2601,7 @@
         <v>128533314</v>
       </c>
       <c r="B20" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>128533312</v>
       </c>
       <c r="B21" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>128533094</v>
       </c>
       <c r="B22" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>128533306</v>
       </c>
       <c r="B23" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>128533307</v>
       </c>
       <c r="B24" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>128533310</v>
       </c>
       <c r="B25" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128533311</v>
       </c>
       <c r="B26" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>128533308</v>
       </c>
       <c r="B27" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>128533305</v>
       </c>
       <c r="B28" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>128533093</v>
       </c>
       <c r="B29" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>128533313</v>
       </c>
       <c r="B30" t="n">
-        <v>92831</v>
+        <v>92836</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>128533303</v>
       </c>
       <c r="B31" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -2386,32 +2386,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128533095</v>
+        <v>128533304</v>
       </c>
       <c r="B18" t="n">
-        <v>92805</v>
+        <v>92811</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406173</v>
+        <v>406143</v>
       </c>
       <c r="R18" t="n">
-        <v>6853701</v>
+        <v>6853912</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2455,12 +2455,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2492,32 +2492,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128533304</v>
+        <v>128533095</v>
       </c>
       <c r="B19" t="n">
-        <v>92811</v>
+        <v>92805</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406143</v>
+        <v>406173</v>
       </c>
       <c r="R19" t="n">
-        <v>6853912</v>
+        <v>6853701</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">

--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -2386,32 +2386,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128533304</v>
+        <v>128533095</v>
       </c>
       <c r="B18" t="n">
-        <v>92811</v>
+        <v>92813</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406143</v>
+        <v>406173</v>
       </c>
       <c r="R18" t="n">
-        <v>6853912</v>
+        <v>6853701</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2455,12 +2455,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2492,32 +2492,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128533095</v>
+        <v>128533304</v>
       </c>
       <c r="B19" t="n">
-        <v>92805</v>
+        <v>92819</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406173</v>
+        <v>406143</v>
       </c>
       <c r="R19" t="n">
-        <v>6853701</v>
+        <v>6853912</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2601,7 +2601,7 @@
         <v>128533314</v>
       </c>
       <c r="B20" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>128533312</v>
       </c>
       <c r="B21" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>128533094</v>
       </c>
       <c r="B22" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>128533306</v>
       </c>
       <c r="B23" t="n">
-        <v>92823</v>
+        <v>92831</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>128533307</v>
       </c>
       <c r="B24" t="n">
-        <v>92805</v>
+        <v>92813</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>128533310</v>
       </c>
       <c r="B25" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128533311</v>
       </c>
       <c r="B26" t="n">
-        <v>92805</v>
+        <v>92813</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>128533308</v>
       </c>
       <c r="B27" t="n">
-        <v>92823</v>
+        <v>92831</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>128533305</v>
       </c>
       <c r="B28" t="n">
-        <v>92823</v>
+        <v>92831</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3552,32 +3552,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128533093</v>
+        <v>128533313</v>
       </c>
       <c r="B29" t="n">
-        <v>92811</v>
+        <v>92844</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3591,13 +3591,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>406203</v>
+        <v>406072</v>
       </c>
       <c r="R29" t="n">
-        <v>6853655</v>
+        <v>6853922</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3621,12 +3621,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3658,32 +3658,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128533313</v>
+        <v>128533093</v>
       </c>
       <c r="B30" t="n">
-        <v>92836</v>
+        <v>92819</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3697,13 +3697,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>406072</v>
+        <v>406203</v>
       </c>
       <c r="R30" t="n">
-        <v>6853922</v>
+        <v>6853655</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3767,7 +3767,7 @@
         <v>128533303</v>
       </c>
       <c r="B31" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44785-2025 artfynd.xlsx
+++ b/artfynd/A 44785-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340171</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031713</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117055988</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533313</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340195</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1321,6 +1351,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340200</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1427,6 +1462,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340254</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1533,6 +1573,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533095</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1639,6 +1684,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533307</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1745,6 +1795,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533311</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1851,6 +1906,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340194</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1957,6 +2017,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340196</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340197</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2169,6 +2239,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340255</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2275,6 +2350,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340256</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2381,6 +2461,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533093</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2487,6 +2572,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533094</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2593,6 +2683,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533303</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2699,6 +2794,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533304</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2805,6 +2905,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533310</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2911,6 +3016,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533312</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3017,6 +3127,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533314</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3123,6 +3238,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340172</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3229,6 +3349,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340198</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3335,6 +3460,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340199</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3441,6 +3571,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340201</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3547,6 +3682,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340202</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3653,6 +3793,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340203</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3759,6 +3904,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533305</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3865,6 +4015,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533306</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3971,6 +4126,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533308</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4077,6 +4237,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031819</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4183,8 +4348,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031617</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>